--- a/results/stress/P4_full_adapted_BASE/results.xlsx
+++ b/results/stress/P4_full_adapted_BASE/results.xlsx
@@ -1606,19 +1606,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1716,7 +1716,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1796,7 +1796,7 @@
         <v>207.9471</v>
       </c>
       <c r="P4" t="n">
-        <v>5.926492350000001</v>
+        <v>5.92649235</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.131628207280301e-14</v>
+        <v>3.552713678800501e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1870,10 +1870,10 @@
         <v>127.3302692500002</v>
       </c>
       <c r="N5" t="n">
-        <v>346.0372000000001</v>
+        <v>346.0372</v>
       </c>
       <c r="O5" t="n">
-        <v>346.0372000000001</v>
+        <v>346.0372</v>
       </c>
       <c r="P5" t="n">
         <v>4.152446400000001</v>
@@ -1888,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>73.1545591166668</v>
+        <v>73.15455911666682</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.105427357601002e-14</v>
+        <v>-1.56319401867222e-13</v>
       </c>
     </row>
     <row r="6">
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-1.13686837721616e-13</v>
       </c>
     </row>
     <row r="7">
@@ -2009,7 +2009,7 @@
         <v>390</v>
       </c>
       <c r="G7" t="n">
-        <v>250.0000000000001</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -2027,19 +2027,19 @@
         <v>214.8949904500004</v>
       </c>
       <c r="M7" t="n">
-        <v>273.3950216500006</v>
+        <v>273.3950216500005</v>
       </c>
       <c r="N7" t="n">
-        <v>453.9474000000002</v>
+        <v>453.9474</v>
       </c>
       <c r="O7" t="n">
-        <v>453.9474000000002</v>
+        <v>453.9474</v>
       </c>
       <c r="P7" t="n">
         <v>5.4473688</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01199999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="R7" t="n">
         <v>48.08219178082192</v>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-1.70530256582424e-13</v>
       </c>
     </row>
   </sheetData>
@@ -4922,7 +4922,7 @@
         <v>30.5031</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L40" t="n">
         <v>64.43003738333343</v>
@@ -4993,7 +4993,7 @@
         <v>30.5031</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L41" t="n">
         <v>73.73376685000011</v>
@@ -5064,7 +5064,7 @@
         <v>30.5031</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L42" t="n">
         <v>83.03749631666679</v>
@@ -5135,7 +5135,7 @@
         <v>30.5031</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L43" t="n">
         <v>92.34122578333347</v>
@@ -5206,7 +5206,7 @@
         <v>30.5031</v>
       </c>
       <c r="K44" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L44" t="n">
         <v>101.6449552500002</v>
@@ -5277,7 +5277,7 @@
         <v>30.5031</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L45" t="n">
         <v>110.9486847166668</v>
@@ -5348,7 +5348,7 @@
         <v>30.5031</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L46" t="n">
         <v>120.2524141833335</v>
@@ -5419,7 +5419,7 @@
         <v>30.5031</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L47" t="n">
         <v>129.5561436500002</v>
@@ -5490,7 +5490,7 @@
         <v>30.5031</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L48" t="n">
         <v>138.8598731166669</v>
@@ -5561,7 +5561,7 @@
         <v>30.5031</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L49" t="n">
         <v>148.1636025833336</v>
@@ -5632,7 +5632,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K50" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L50" t="n">
         <v>161.2939960166669</v>
@@ -5703,7 +5703,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L51" t="n">
         <v>168.5910561166669</v>
@@ -5774,7 +5774,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L52" t="n">
         <v>175.8881162166669</v>
@@ -5845,7 +5845,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L53" t="n">
         <v>183.1851763166669</v>
@@ -5916,7 +5916,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K54" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L54" t="n">
         <v>190.482236416667</v>
@@ -5987,7 +5987,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L55" t="n">
         <v>197.779296516667</v>
@@ -6058,7 +6058,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K56" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L56" t="n">
         <v>205.076356616667</v>
@@ -6129,7 +6129,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L57" t="n">
         <v>212.373416716667</v>
@@ -6200,7 +6200,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L58" t="n">
         <v>219.670476816667</v>
@@ -6271,7 +6271,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L59" t="n">
         <v>226.967536916667</v>
@@ -6342,7 +6342,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K60" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L60" t="n">
         <v>234.264597016667</v>
@@ -6413,7 +6413,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L61" t="n">
         <v>241.561657116667</v>
@@ -6478,13 +6478,13 @@
         <v>214.8949904500004</v>
       </c>
       <c r="I62" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J62" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L62" t="n">
         <v>252.2699930500004</v>
@@ -6549,16 +6549,16 @@
         <v>219.7699930500004</v>
       </c>
       <c r="I63" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J63" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L63" t="n">
-        <v>257.1449956500004</v>
+        <v>257.1449956500003</v>
       </c>
       <c r="M63" t="n">
         <v>32.5</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>224.6449956500004</v>
+        <v>224.6449956500003</v>
       </c>
       <c r="T63" t="n">
         <v>13.33244966100002</v>
@@ -6617,16 +6617,16 @@
         <v>0.012</v>
       </c>
       <c r="H64" t="n">
-        <v>224.6449956500004</v>
+        <v>224.6449956500003</v>
       </c>
       <c r="I64" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J64" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L64" t="n">
         <v>262.0199982500004</v>
@@ -6691,13 +6691,13 @@
         <v>229.5199982500004</v>
       </c>
       <c r="I65" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J65" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L65" t="n">
         <v>266.8950008500004</v>
@@ -6762,13 +6762,13 @@
         <v>234.3950008500004</v>
       </c>
       <c r="I66" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J66" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L66" t="n">
         <v>271.7700034500004</v>
@@ -6795,7 +6795,7 @@
         <v>239.2700034500004</v>
       </c>
       <c r="T66" t="n">
-        <v>14.20995012900003</v>
+        <v>14.20995012900002</v>
       </c>
       <c r="U66" t="n">
         <v>15.83333333333333</v>
@@ -6833,16 +6833,16 @@
         <v>239.2700034500004</v>
       </c>
       <c r="I67" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J67" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L67" t="n">
-        <v>276.6450060500005</v>
+        <v>276.6450060500004</v>
       </c>
       <c r="M67" t="n">
         <v>32.5</v>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>244.1450060500005</v>
+        <v>244.1450060500004</v>
       </c>
       <c r="T67" t="n">
         <v>14.50245028500002</v>
@@ -6901,19 +6901,19 @@
         <v>0.012</v>
       </c>
       <c r="H68" t="n">
-        <v>244.1450060500005</v>
+        <v>244.1450060500004</v>
       </c>
       <c r="I68" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J68" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L68" t="n">
-        <v>281.5200086500005</v>
+        <v>281.5200086500004</v>
       </c>
       <c r="M68" t="n">
         <v>32.5</v>
@@ -6934,10 +6934,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>249.0200086500005</v>
+        <v>249.0200086500004</v>
       </c>
       <c r="T68" t="n">
-        <v>14.79495044100003</v>
+        <v>14.79495044100002</v>
       </c>
       <c r="U68" t="n">
         <v>15.83333333333333</v>
@@ -6972,19 +6972,19 @@
         <v>0.012</v>
       </c>
       <c r="H69" t="n">
-        <v>249.0200086500005</v>
+        <v>249.0200086500004</v>
       </c>
       <c r="I69" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J69" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L69" t="n">
-        <v>286.3950112500005</v>
+        <v>286.3950112500004</v>
       </c>
       <c r="M69" t="n">
         <v>32.5</v>
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>253.8950112500005</v>
+        <v>253.8950112500004</v>
       </c>
       <c r="T69" t="n">
         <v>15.08745059700003</v>
@@ -7043,16 +7043,16 @@
         <v>0.012</v>
       </c>
       <c r="H70" t="n">
-        <v>253.8950112500005</v>
+        <v>253.8950112500004</v>
       </c>
       <c r="I70" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J70" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K70" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L70" t="n">
         <v>291.2700138500005</v>
@@ -7117,13 +7117,13 @@
         <v>258.7700138500005</v>
       </c>
       <c r="I71" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J71" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K71" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L71" t="n">
         <v>296.1450164500005</v>
@@ -7188,13 +7188,13 @@
         <v>263.6450164500005</v>
       </c>
       <c r="I72" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J72" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L72" t="n">
         <v>301.0200190500005</v>
@@ -7259,16 +7259,16 @@
         <v>268.5200190500005</v>
       </c>
       <c r="I73" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="J73" t="n">
-        <v>37.82895000000001</v>
+        <v>37.82895</v>
       </c>
       <c r="K73" t="n">
-        <v>0.4539474000000001</v>
+        <v>0.4539474</v>
       </c>
       <c r="L73" t="n">
-        <v>305.8950216500006</v>
+        <v>305.8950216500005</v>
       </c>
       <c r="M73" t="n">
         <v>32.5</v>
@@ -7289,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>273.3950216500006</v>
+        <v>273.3950216500005</v>
       </c>
       <c r="T73" t="n">
         <v>16.25745122100003</v>
@@ -8817,10 +8817,10 @@
         <v>56.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>56.03720000000001</v>
+        <v>56.0372</v>
       </c>
       <c r="N20" t="n">
-        <v>56.03720000000001</v>
+        <v>56.0372</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -10854,7 +10854,7 @@
         <v>120</v>
       </c>
       <c r="K18" t="n">
-        <v>99.76999305000038</v>
+        <v>99.76999305000035</v>
       </c>
     </row>
     <row r="19">
@@ -10890,13 +10890,13 @@
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>224.6449956500004</v>
+        <v>224.6449956500003</v>
       </c>
       <c r="J19" t="n">
         <v>120</v>
       </c>
       <c r="K19" t="n">
-        <v>104.6449956500004</v>
+        <v>104.6449956500003</v>
       </c>
     </row>
     <row r="20">
@@ -11058,13 +11058,13 @@
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>244.1450060500005</v>
+        <v>244.1450060500004</v>
       </c>
       <c r="J23" t="n">
         <v>120</v>
       </c>
       <c r="K23" t="n">
-        <v>124.1450060500005</v>
+        <v>124.1450060500004</v>
       </c>
     </row>
     <row r="24">
@@ -11100,13 +11100,13 @@
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>249.0200086500005</v>
+        <v>249.0200086500004</v>
       </c>
       <c r="J24" t="n">
         <v>120</v>
       </c>
       <c r="K24" t="n">
-        <v>129.0200086500005</v>
+        <v>129.0200086500004</v>
       </c>
     </row>
     <row r="25">
@@ -11142,13 +11142,13 @@
         <v>8</v>
       </c>
       <c r="I25" t="n">
-        <v>253.8950112500005</v>
+        <v>253.8950112500004</v>
       </c>
       <c r="J25" t="n">
         <v>120</v>
       </c>
       <c r="K25" t="n">
-        <v>133.8950112500005</v>
+        <v>133.8950112500004</v>
       </c>
     </row>
     <row r="26">
@@ -11310,13 +11310,13 @@
         <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>273.3950216500006</v>
+        <v>273.3950216500005</v>
       </c>
       <c r="J29" t="n">
         <v>120</v>
       </c>
       <c r="K29" t="n">
-        <v>153.3950216500006</v>
+        <v>153.3950216500005</v>
       </c>
     </row>
   </sheetData>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>273.3950216500006</v>
+        <v>273.3950216500005</v>
       </c>
       <c r="G70" t="n">
         <v>120</v>
@@ -24517,7 +24517,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>950.0000000000001</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -24537,7 +24537,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -24597,7 +24597,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.414203263791552</v>
+        <v>7.414203263791551</v>
       </c>
     </row>
     <row r="12">
@@ -24617,7 +24617,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -24737,7 +24737,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>556.2965700000001</v>
+        <v>556.29657</v>
       </c>
     </row>
     <row r="19">
@@ -24837,7 +24837,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>273.3950216500006</v>
+        <v>273.3950216500005</v>
       </c>
     </row>
     <row r="24">

--- a/results/stress/P4_full_adapted_BASE/results.xlsx
+++ b/results/stress/P4_full_adapted_BASE/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>25 / 0 / 3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -821,7 +965,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -836,7 +980,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -854,7 +998,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -869,7 +1013,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -886,7 +1030,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,7 +1045,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -918,7 +1062,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -933,7 +1077,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -950,7 +1094,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -965,7 +1109,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -982,7 +1126,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -997,7 +1141,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1158,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1029,7 +1173,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1190,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1061,7 +1205,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1222,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1093,7 +1237,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1254,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1125,7 +1269,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1286,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1157,7 +1301,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1318,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1189,7 +1333,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1350,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1221,7 +1365,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1382,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1253,7 +1397,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1414,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1285,7 +1429,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1446,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1317,7 +1461,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1478,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1349,7 +1493,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1510,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1381,7 +1525,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1542,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1413,7 +1557,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1574,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1445,7 +1589,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10310,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stock after inflow 120.252 t exceeds ZBO modernization capacity 120.0 t within 2038-09 (before withdrawals)</t>
+          <t>запас после поступления 120.252 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-09 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10208,7 +10352,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stock after inflow 129.556 t exceeds ZBO modernization capacity 120.0 t within 2038-10 (before withdrawals)</t>
+          <t>запас после поступления 129.556 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-10 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10250,7 +10394,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stock after inflow 138.860 t exceeds ZBO modernization capacity 120.0 t within 2038-11 (before withdrawals)</t>
+          <t>запас после поступления 138.860 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-11 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10292,7 +10436,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>end-of-month stock 127.330 t exceeds ZBO modernization capacity 120.0 t in 2038-12</t>
+          <t>запас на конец месяца 127.330 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-12</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10334,7 +10478,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>end-of-month stock 134.627 t exceeds ZBO modernization capacity 120.0 t in 2039-01</t>
+          <t>запас на конец месяца 134.627 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10376,7 +10520,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>end-of-month stock 141.924 t exceeds ZBO modernization capacity 120.0 t in 2039-02</t>
+          <t>запас на конец месяца 141.924 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -10418,7 +10562,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>end-of-month stock 149.221 t exceeds ZBO modernization capacity 120.0 t in 2039-03</t>
+          <t>запас на конец месяца 149.221 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -10460,7 +10604,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>end-of-month stock 156.519 t exceeds ZBO modernization capacity 120.0 t in 2039-04</t>
+          <t>запас на конец месяца 156.519 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -10502,7 +10646,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>end-of-month stock 163.816 t exceeds ZBO modernization capacity 120.0 t in 2039-05</t>
+          <t>запас на конец месяца 163.816 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -10544,7 +10688,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>end-of-month stock 171.113 t exceeds ZBO modernization capacity 120.0 t in 2039-06</t>
+          <t>запас на конец месяца 171.113 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -10586,7 +10730,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>end-of-month stock 178.410 t exceeds ZBO modernization capacity 120.0 t in 2039-07</t>
+          <t>запас на конец месяца 178.410 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -10628,7 +10772,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>end-of-month stock 185.707 t exceeds ZBO modernization capacity 120.0 t in 2039-08</t>
+          <t>запас на конец месяца 185.707 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -10670,7 +10814,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>end-of-month stock 193.004 t exceeds ZBO modernization capacity 120.0 t in 2039-09</t>
+          <t>запас на конец месяца 193.004 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -10712,7 +10856,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>end-of-month stock 200.301 t exceeds ZBO modernization capacity 120.0 t in 2039-10</t>
+          <t>запас на конец месяца 200.301 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -10754,7 +10898,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>end-of-month stock 207.598 t exceeds ZBO modernization capacity 120.0 t in 2039-11</t>
+          <t>запас на конец месяца 207.598 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -10796,7 +10940,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>end-of-month stock 214.895 t exceeds ZBO modernization capacity 120.0 t in 2039-12</t>
+          <t>запас на конец месяца 214.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -10838,7 +10982,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>end-of-month stock 219.770 t exceeds ZBO modernization capacity 120.0 t in 2040-01</t>
+          <t>запас на конец месяца 219.770 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -10880,7 +11024,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>end-of-month stock 224.645 t exceeds ZBO modernization capacity 120.0 t in 2040-02</t>
+          <t>запас на конец месяца 224.645 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -10922,7 +11066,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>end-of-month stock 229.520 t exceeds ZBO modernization capacity 120.0 t in 2040-03</t>
+          <t>запас на конец месяца 229.520 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -10964,7 +11108,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>end-of-month stock 234.395 t exceeds ZBO modernization capacity 120.0 t in 2040-04</t>
+          <t>запас на конец месяца 234.395 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -11006,7 +11150,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>end-of-month stock 239.270 t exceeds ZBO modernization capacity 120.0 t in 2040-05</t>
+          <t>запас на конец месяца 239.270 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -11048,7 +11192,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>end-of-month stock 244.145 t exceeds ZBO modernization capacity 120.0 t in 2040-06</t>
+          <t>запас на конец месяца 244.145 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -11090,7 +11234,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>end-of-month stock 249.020 t exceeds ZBO modernization capacity 120.0 t in 2040-07</t>
+          <t>запас на конец месяца 249.020 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -11132,7 +11276,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>end-of-month stock 253.895 t exceeds ZBO modernization capacity 120.0 t in 2040-08</t>
+          <t>запас на конец месяца 253.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -11174,7 +11318,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>end-of-month stock 258.770 t exceeds ZBO modernization capacity 120.0 t in 2040-09</t>
+          <t>запас на конец месяца 258.770 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -11216,7 +11360,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>end-of-month stock 263.645 t exceeds ZBO modernization capacity 120.0 t in 2040-10</t>
+          <t>запас на конец месяца 263.645 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -11258,7 +11402,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>end-of-month stock 268.520 t exceeds ZBO modernization capacity 120.0 t in 2040-11</t>
+          <t>запас на конец месяца 268.520 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -11300,7 +11444,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>end-of-month stock 273.395 t exceeds ZBO modernization capacity 120.0 t in 2040-12</t>
+          <t>запас на конец месяца 273.395 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -12697,7 +12841,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -12710,7 +12854,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12890,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -12759,7 +12903,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12939,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12808,7 +12952,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12988,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12857,7 +13001,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12893,7 +13037,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12906,7 +13050,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12942,7 +13086,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12955,7 +13099,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13843,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -13709,7 +13853,7 @@
         <v/>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -14130,7 +14274,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -14140,7 +14284,7 @@
         <v/>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -15164,7 +15308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15233,6 +15377,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15288,6 +15437,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15343,6 +15497,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15398,6 +15557,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15453,6 +15617,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15508,6 +15677,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15563,6 +15737,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15618,6 +15797,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15673,6 +15857,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15728,6 +15917,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15783,6 +15977,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15838,6 +16037,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15893,6 +16097,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15948,6 +16157,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16003,6 +16217,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16058,6 +16277,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16113,6 +16337,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16168,6 +16397,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16223,6 +16457,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16278,6 +16517,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16333,6 +16577,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16388,6 +16637,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16443,6 +16697,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16498,6 +16757,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16553,6 +16817,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16608,6 +16877,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16648,11 +16922,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2035-01</t>
+          <t>2037-01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -16661,7 +16935,12 @@
         </is>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -16718,6 +16997,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16758,11 +17042,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2035-02</t>
+          <t>2037-02</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -16771,7 +17055,12 @@
         </is>
       </c>
       <c r="M29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -16828,6 +17117,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16868,11 +17162,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2035-03</t>
+          <t>2037-03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -16881,7 +17175,12 @@
         </is>
       </c>
       <c r="M31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -16938,6 +17237,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16978,11 +17282,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2035-04</t>
+          <t>2037-04</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -16991,7 +17295,12 @@
         </is>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -17048,6 +17357,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17088,11 +17402,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2035-05</t>
+          <t>2037-05</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -17101,7 +17415,12 @@
         </is>
       </c>
       <c r="M35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -17158,6 +17477,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17198,11 +17522,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2035-06</t>
+          <t>2037-06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -17211,7 +17535,12 @@
         </is>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -17268,6 +17597,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17308,11 +17642,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2035-07</t>
+          <t>2037-07</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -17321,7 +17655,12 @@
         </is>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -17378,6 +17717,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17418,11 +17762,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -17431,7 +17775,12 @@
         </is>
       </c>
       <c r="M41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -17488,6 +17837,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -17528,11 +17882,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2035-09</t>
+          <t>2037-09</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -17541,7 +17895,12 @@
         </is>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -17598,6 +17957,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17638,11 +18002,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2035-10</t>
+          <t>2037-10</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -17651,7 +18015,12 @@
         </is>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -17708,6 +18077,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17748,11 +18122,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2035-11</t>
+          <t>2037-11</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -17761,7 +18135,12 @@
         </is>
       </c>
       <c r="M47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -17818,6 +18197,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17858,11 +18242,11 @@
         <v>1.495591666666667</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2035-12</t>
+          <t>2037-12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -17871,7 +18255,12 @@
         </is>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -17928,6 +18317,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17968,11 +18362,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2036-01</t>
+          <t>2038-01</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -17981,7 +18375,12 @@
         </is>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -18038,6 +18437,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -18078,11 +18482,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2036-02</t>
+          <t>2038-02</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -18091,7 +18495,12 @@
         </is>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -18148,6 +18557,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -18188,11 +18602,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2036-03</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -18201,7 +18615,12 @@
         </is>
       </c>
       <c r="M55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -18258,6 +18677,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -18313,6 +18737,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18353,11 +18782,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J58" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2036-04</t>
+          <t>2038-04</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -18366,7 +18795,12 @@
         </is>
       </c>
       <c r="M58" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -18423,6 +18857,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18478,6 +18917,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18518,11 +18962,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2036-05</t>
+          <t>2038-05</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -18531,7 +18975,12 @@
         </is>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -18588,6 +19037,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18643,6 +19097,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -18683,11 +19142,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J64" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2036-06</t>
+          <t>2038-06</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -18696,7 +19155,12 @@
         </is>
       </c>
       <c r="M64" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -18753,6 +19217,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18808,6 +19277,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18848,11 +19322,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J67" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2036-07</t>
+          <t>2038-07</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -18861,7 +19335,12 @@
         </is>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -18918,6 +19397,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18973,6 +19457,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19013,11 +19502,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J70" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -19026,7 +19515,12 @@
         </is>
       </c>
       <c r="M70" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -19083,6 +19577,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -19138,6 +19637,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -19178,11 +19682,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2036-09</t>
+          <t>2038-09</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -19191,7 +19695,12 @@
         </is>
       </c>
       <c r="M73" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -19248,6 +19757,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -19303,6 +19817,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -19343,11 +19862,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2036-10</t>
+          <t>2038-10</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -19356,7 +19875,12 @@
         </is>
       </c>
       <c r="M76" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -19413,6 +19937,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -19468,6 +19997,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -19508,11 +20042,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J79" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2036-11</t>
+          <t>2038-11</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -19521,7 +20055,12 @@
         </is>
       </c>
       <c r="M79" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -19578,6 +20117,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19633,6 +20177,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19673,11 +20222,11 @@
         <v>4.669766666666667</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2036-12</t>
+          <t>2038-12</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -19686,7 +20235,12 @@
         </is>
       </c>
       <c r="M82" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -19743,6 +20297,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19798,6 +20357,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19838,20 +20402,25 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t>2039-01</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t>2037-01</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>2037-01</t>
-        </is>
-      </c>
       <c r="M85" t="b">
         <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -19908,6 +20477,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19963,6 +20537,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -20003,11 +20582,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2037-02</t>
+          <t>2039-02</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -20017,6 +20596,11 @@
       </c>
       <c r="M88" t="b">
         <v>1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -20073,6 +20657,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -20128,6 +20717,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -20168,11 +20762,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2037-03</t>
+          <t>2039-03</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -20182,6 +20776,11 @@
       </c>
       <c r="M91" t="b">
         <v>1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -20238,6 +20837,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -20293,6 +20897,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -20333,11 +20942,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2037-04</t>
+          <t>2039-04</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -20347,6 +20956,11 @@
       </c>
       <c r="M94" t="b">
         <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -20403,6 +21017,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -20458,6 +21077,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -20498,11 +21122,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2037-05</t>
+          <t>2039-05</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -20512,6 +21136,11 @@
       </c>
       <c r="M97" t="b">
         <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -20568,6 +21197,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -20623,6 +21257,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -20663,11 +21302,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J100" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2037-06</t>
+          <t>2039-06</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -20677,6 +21316,11 @@
       </c>
       <c r="M100" t="b">
         <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -20733,6 +21377,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -20788,6 +21437,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -20828,11 +21482,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2037-07</t>
+          <t>2039-07</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -20842,6 +21496,11 @@
       </c>
       <c r="M103" t="b">
         <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -20898,6 +21557,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -20953,6 +21617,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20993,11 +21662,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J106" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2039-08</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -21007,6 +21676,11 @@
       </c>
       <c r="M106" t="b">
         <v>1</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -21063,6 +21737,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -21118,6 +21797,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -21158,11 +21842,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J109" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2037-09</t>
+          <t>2039-09</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -21172,6 +21856,11 @@
       </c>
       <c r="M109" t="b">
         <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -21228,6 +21917,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -21283,6 +21977,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -21323,11 +22022,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J112" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2037-10</t>
+          <t>2039-10</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -21337,6 +22036,11 @@
       </c>
       <c r="M112" t="b">
         <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -21393,6 +22097,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -21448,6 +22157,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -21488,11 +22202,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J115" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2037-11</t>
+          <t>2039-11</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -21502,6 +22216,11 @@
       </c>
       <c r="M115" t="b">
         <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -21558,6 +22277,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -21613,6 +22337,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -21653,11 +22382,11 @@
         <v>8.542908333333333</v>
       </c>
       <c r="J118" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2037-12</t>
+          <t>2039-12</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -21667,6 +22396,11 @@
       </c>
       <c r="M118" t="b">
         <v>1</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -21723,6 +22457,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -21778,6 +22517,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -21833,6 +22577,11 @@
       <c r="M121" t="b">
         <v>1</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -21873,11 +22622,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J122" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2038-01</t>
+          <t>2040-01</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -21887,6 +22636,11 @@
       </c>
       <c r="M122" t="b">
         <v>1</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -21943,6 +22697,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -21998,6 +22757,11 @@
       <c r="M124" t="b">
         <v>1</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -22053,6 +22817,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -22093,11 +22862,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J126" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2038-02</t>
+          <t>2040-02</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -22107,6 +22876,11 @@
       </c>
       <c r="M126" t="b">
         <v>1</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -22163,6 +22937,11 @@
       <c r="M127" t="b">
         <v>1</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -22218,6 +22997,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -22273,6 +23057,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -22313,11 +23102,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2038-03</t>
+          <t>2040-03</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -22327,6 +23116,11 @@
       </c>
       <c r="M130" t="b">
         <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -22383,6 +23177,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -22438,6 +23237,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -22493,6 +23297,11 @@
       <c r="M133" t="b">
         <v>1</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -22533,11 +23342,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J134" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2038-04</t>
+          <t>2040-04</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -22547,6 +23356,11 @@
       </c>
       <c r="M134" t="b">
         <v>1</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -22603,6 +23417,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -22658,6 +23477,11 @@
       <c r="M136" t="b">
         <v>1</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -22713,6 +23537,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -22753,11 +23582,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J138" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2038-05</t>
+          <t>2040-05</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -22767,6 +23596,11 @@
       </c>
       <c r="M138" t="b">
         <v>1</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -22823,6 +23657,11 @@
       <c r="M139" t="b">
         <v>1</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -22878,6 +23717,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -22933,6 +23777,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -22973,11 +23822,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J142" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2038-06</t>
+          <t>2040-06</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -22987,6 +23836,11 @@
       </c>
       <c r="M142" t="b">
         <v>1</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -23043,6 +23897,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -23098,6 +23957,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -23153,6 +24017,11 @@
       <c r="M145" t="b">
         <v>1</v>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -23193,11 +24062,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J146" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2038-07</t>
+          <t>2040-07</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -23207,6 +24076,11 @@
       </c>
       <c r="M146" t="b">
         <v>1</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -23263,6 +24137,11 @@
       <c r="M147" t="b">
         <v>1</v>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -23318,6 +24197,11 @@
       <c r="M148" t="b">
         <v>1</v>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -23373,6 +24257,11 @@
       <c r="M149" t="b">
         <v>1</v>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -23413,11 +24302,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J150" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2040-08</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -23427,6 +24316,11 @@
       </c>
       <c r="M150" t="b">
         <v>1</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -23483,6 +24377,11 @@
       <c r="M151" t="b">
         <v>1</v>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -23538,6 +24437,11 @@
       <c r="M152" t="b">
         <v>1</v>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -23593,6 +24497,11 @@
       <c r="M153" t="b">
         <v>1</v>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -23633,11 +24542,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J154" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2038-09</t>
+          <t>2040-09</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -23647,6 +24556,11 @@
       </c>
       <c r="M154" t="b">
         <v>1</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -23703,6 +24617,11 @@
       <c r="M155" t="b">
         <v>1</v>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -23758,6 +24677,11 @@
       <c r="M156" t="b">
         <v>1</v>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -23813,6 +24737,11 @@
       <c r="M157" t="b">
         <v>1</v>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -23853,11 +24782,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J158" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2038-10</t>
+          <t>2040-10</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -23867,6 +24796,11 @@
       </c>
       <c r="M158" t="b">
         <v>1</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -23923,6 +24857,11 @@
       <c r="M159" t="b">
         <v>1</v>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -23978,6 +24917,11 @@
       <c r="M160" t="b">
         <v>1</v>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -24033,6 +24977,11 @@
       <c r="M161" t="b">
         <v>1</v>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -24073,11 +25022,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J162" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2038-11</t>
+          <t>2040-11</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -24087,6 +25036,11 @@
       </c>
       <c r="M162" t="b">
         <v>1</v>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -24143,6 +25097,11 @@
       <c r="M163" t="b">
         <v>1</v>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -24198,6 +25157,11 @@
       <c r="M164" t="b">
         <v>1</v>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -24253,6 +25217,11 @@
       <c r="M165" t="b">
         <v>1</v>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -24293,11 +25262,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J166" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2038-12</t>
+          <t>2040-12</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -24307,6 +25276,11 @@
       </c>
       <c r="M166" t="b">
         <v>1</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -24362,6 +25336,11 @@
       </c>
       <c r="M167" t="b">
         <v>1</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -24957,7 +25936,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/results/stress/P4_full_adapted_BASE/results.xlsx
+++ b/results/stress/P4_full_adapted_BASE/results.xlsx
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1590,6 +1590,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -12830,18 +12863,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -12854,7 +12887,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12879,18 +12912,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -12903,7 +12936,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12928,18 +12961,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12952,7 +12985,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12977,18 +13010,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -13001,7 +13034,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13026,18 +13059,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -13050,7 +13083,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13075,18 +13108,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -13099,7 +13132,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13124,7 +13157,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -13148,7 +13181,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13392,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -13383,7 +13416,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13594,11 +13627,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>35.44551565000008</v>
+        <v>27.71964825000006</v>
       </c>
       <c r="G45" t="n">
         <v>70</v>
@@ -13618,7 +13651,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13960,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -13951,7 +13984,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14391,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -14382,7 +14415,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14789,7 +14822,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -14813,7 +14846,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/stress/P4_full_adapted_BASE/results.xlsx
+++ b/results/stress/P4_full_adapted_BASE/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/stress/P4_full_adapted_BASE/results.xlsx
+++ b/results/stress/P4_full_adapted_BASE/results.xlsx
@@ -7585,7 +7585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7694,6 +7694,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7769,6 +7774,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7844,6 +7852,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7919,6 +7930,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7994,6 +8008,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8069,6 +8086,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8144,6 +8164,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8219,6 +8242,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8294,6 +8320,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8369,6 +8398,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8444,6 +8476,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8519,6 +8554,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8594,6 +8632,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8669,6 +8710,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8744,6 +8788,9 @@
       <c r="U15" t="n">
         <v>5.3844</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8819,6 +8866,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8894,6 +8944,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8969,6 +9022,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9044,6 +9100,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9119,6 +9178,9 @@
       <c r="U20" t="n">
         <v>16.8114</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9194,6 +9256,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9269,6 +9334,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9344,6 +9412,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9419,6 +9490,9 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9494,6 +9568,9 @@
       <c r="U25" t="n">
         <v>30.7545</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9569,6 +9646,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9644,6 +9724,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9719,6 +9802,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9794,6 +9880,9 @@
       <c r="U29" t="n">
         <v>2.0922</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9869,6 +9958,9 @@
       <c r="U30" t="n">
         <v>39</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9944,6 +10036,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10017,6 +10112,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10031,7 +10129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10095,6 +10193,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10137,6 +10240,9 @@
       <c r="L2" t="n">
         <v>360</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10179,6 +10285,9 @@
       <c r="L3" t="n">
         <v>1610</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10221,6 +10330,9 @@
       <c r="L4" t="n">
         <v>1790</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10263,6 +10375,9 @@
       <c r="L5" t="n">
         <v>1790</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10305,6 +10420,9 @@
       <c r="L6" t="n">
         <v>1790</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10346,6 +10464,9 @@
       </c>
       <c r="L7" t="n">
         <v>1790</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -25486,7 +25607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25924,11 +26045,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -25944,11 +26065,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>273.3950216500005</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -25964,11 +26085,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>273.3950216500005</v>
       </c>
     </row>
     <row r="25">
@@ -25984,11 +26105,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -26004,11 +26125,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -26024,11 +26145,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -26044,11 +26165,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>79</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -26064,10 +26185,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>76</v>
       </c>
     </row>

--- a/results/stress/P4_full_adapted_BASE/results.xlsx
+++ b/results/stress/P4_full_adapted_BASE/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25 / 0 / 3</t>
+          <t>53 / 0 / 0</t>
         </is>
       </c>
     </row>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -917,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,7 +1443,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1461,24 +1463,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1488,29 +1490,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1520,29 +1522,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1552,176 +1554,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2458,6 +2603,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2530,6 +2685,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2601,6 +2762,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2672,6 +2839,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2743,6 +2916,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2814,6 +2993,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2885,6 +3070,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2956,6 +3147,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3027,6 +3224,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3098,6 +3301,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3169,6 +3378,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3240,6 +3455,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3311,6 +3532,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3382,6 +3609,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3453,6 +3686,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3524,6 +3763,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3595,6 +3840,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3666,6 +3917,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3737,6 +3994,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3808,6 +4071,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3879,6 +4148,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3950,6 +4225,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4021,6 +4302,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4092,6 +4379,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4163,6 +4456,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4234,6 +4533,12 @@
         <v>1.426968181250004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.97403137500007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4305,6 +4610,12 @@
         <v>1.469915583750004</v>
       </c>
       <c r="U27" t="n">
+        <v>40.68982141666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4376,6 +4687,12 @@
         <v>1.512862986250004</v>
       </c>
       <c r="U28" t="n">
+        <v>41.4056114583334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4447,6 +4764,12 @@
         <v>1.555810388750004</v>
       </c>
       <c r="U29" t="n">
+        <v>42.12140150000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4518,6 +4841,12 @@
         <v>1.598757791250004</v>
       </c>
       <c r="U30" t="n">
+        <v>42.83719154166673</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4589,6 +4918,12 @@
         <v>1.641705193750004</v>
       </c>
       <c r="U31" t="n">
+        <v>43.5529815833334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4660,6 +4995,12 @@
         <v>1.701808232000004</v>
       </c>
       <c r="U32" t="n">
+        <v>44.84062615000006</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4731,6 +5072,12 @@
         <v>1.779066906000004</v>
       </c>
       <c r="U33" t="n">
+        <v>46.12827071666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4802,6 +5149,12 @@
         <v>1.856325580000004</v>
       </c>
       <c r="U34" t="n">
+        <v>47.4159152833334</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4873,6 +5226,12 @@
         <v>1.933584254000004</v>
       </c>
       <c r="U35" t="n">
+        <v>48.70355985000008</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4944,6 +5303,12 @@
         <v>2.010842928000005</v>
       </c>
       <c r="U36" t="n">
+        <v>49.99120441666675</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5015,6 +5380,12 @@
         <v>2.088101602000005</v>
       </c>
       <c r="U37" t="n">
+        <v>51.27884898333342</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5086,6 +5457,12 @@
         <v>2.109442823000005</v>
       </c>
       <c r="U38" t="n">
+        <v>55.70257845000008</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5157,6 +5534,12 @@
         <v>2.074866591000005</v>
       </c>
       <c r="U39" t="n">
+        <v>55.12630791666675</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5228,6 +5611,12 @@
         <v>2.336690359000005</v>
       </c>
       <c r="U40" t="n">
+        <v>64.43003738333341</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5299,6 +5688,12 @@
         <v>2.894914127000006</v>
       </c>
       <c r="U41" t="n">
+        <v>73.73376685000009</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5370,6 +5765,12 @@
         <v>3.453137895000007</v>
       </c>
       <c r="U42" t="n">
+        <v>83.03749631666678</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5441,6 +5842,12 @@
         <v>4.011361663000008</v>
       </c>
       <c r="U43" t="n">
+        <v>92.34122578333346</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5512,6 +5919,12 @@
         <v>4.569585431000009</v>
       </c>
       <c r="U44" t="n">
+        <v>101.6449552500001</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5583,6 +5996,12 @@
         <v>5.127809199000009</v>
       </c>
       <c r="U45" t="n">
+        <v>110.9486847166668</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5654,6 +6073,12 @@
         <v>5.686032967000011</v>
       </c>
       <c r="U46" t="n">
+        <v>120.2524141833335</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5725,6 +6150,12 @@
         <v>6.244256735000011</v>
       </c>
       <c r="U47" t="n">
+        <v>129.5561436500002</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5796,6 +6227,12 @@
         <v>6.802480503000012</v>
       </c>
       <c r="U48" t="n">
+        <v>138.8598731166669</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5867,6 +6304,12 @@
         <v>7.360704271000013</v>
       </c>
       <c r="U49" t="n">
+        <v>148.1636025833336</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5938,6 +6381,12 @@
         <v>7.858727958000014</v>
       </c>
       <c r="U50" t="n">
+        <v>161.2939960166669</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6009,6 +6458,12 @@
         <v>8.296551564000016</v>
       </c>
       <c r="U51" t="n">
+        <v>168.5910561166669</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6080,6 +6535,12 @@
         <v>8.734375170000016</v>
       </c>
       <c r="U52" t="n">
+        <v>175.8881162166669</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6151,6 +6612,12 @@
         <v>9.172198776000016</v>
       </c>
       <c r="U53" t="n">
+        <v>183.1851763166669</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6222,6 +6689,12 @@
         <v>9.610022382000016</v>
       </c>
       <c r="U54" t="n">
+        <v>190.482236416667</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6293,6 +6766,12 @@
         <v>10.04784598800002</v>
       </c>
       <c r="U55" t="n">
+        <v>197.779296516667</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6364,6 +6843,12 @@
         <v>10.48566959400002</v>
       </c>
       <c r="U56" t="n">
+        <v>205.076356616667</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6435,6 +6920,12 @@
         <v>10.92349320000002</v>
       </c>
       <c r="U57" t="n">
+        <v>212.373416716667</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6506,6 +6997,12 @@
         <v>11.36131680600002</v>
       </c>
       <c r="U58" t="n">
+        <v>219.670476816667</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6577,6 +7074,12 @@
         <v>11.79914041200002</v>
       </c>
       <c r="U59" t="n">
+        <v>226.967536916667</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6648,6 +7151,12 @@
         <v>12.23696401800002</v>
       </c>
       <c r="U60" t="n">
+        <v>234.264597016667</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6719,6 +7228,12 @@
         <v>12.67478762400002</v>
       </c>
       <c r="U61" t="n">
+        <v>241.561657116667</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6790,6 +7305,12 @@
         <v>13.03994950500002</v>
       </c>
       <c r="U62" t="n">
+        <v>252.2699930500004</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6861,6 +7382,12 @@
         <v>13.33244966100002</v>
       </c>
       <c r="U63" t="n">
+        <v>257.1449956500003</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6932,6 +7459,12 @@
         <v>13.62494981700002</v>
       </c>
       <c r="U64" t="n">
+        <v>262.0199982500004</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7003,6 +7536,12 @@
         <v>13.91744997300002</v>
       </c>
       <c r="U65" t="n">
+        <v>266.8950008500004</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7074,6 +7613,12 @@
         <v>14.20995012900002</v>
       </c>
       <c r="U66" t="n">
+        <v>271.7700034500004</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7145,6 +7690,12 @@
         <v>14.50245028500002</v>
       </c>
       <c r="U67" t="n">
+        <v>276.6450060500004</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7216,6 +7767,12 @@
         <v>14.79495044100002</v>
       </c>
       <c r="U68" t="n">
+        <v>281.5200086500004</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7287,6 +7844,12 @@
         <v>15.08745059700003</v>
       </c>
       <c r="U69" t="n">
+        <v>286.3950112500004</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7358,6 +7921,12 @@
         <v>15.37995075300003</v>
       </c>
       <c r="U70" t="n">
+        <v>291.2700138500005</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7429,6 +7998,12 @@
         <v>15.67245090900003</v>
       </c>
       <c r="U71" t="n">
+        <v>296.1450164500005</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7500,6 +8075,12 @@
         <v>15.96495106500003</v>
       </c>
       <c r="U72" t="n">
+        <v>301.0200190500005</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7571,6 +8152,12 @@
         <v>16.25745122100003</v>
       </c>
       <c r="U73" t="n">
+        <v>305.8950216500005</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10220,7 +10807,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10229,13 +10816,13 @@
         <v>360</v>
       </c>
       <c r="I2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="L2" t="n">
         <v>360</v>
@@ -10480,7 +11067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10558,12 +11145,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>запас после поступления 120.252 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-09 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 120.252 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-09 (поставка одной партией в начале месяца; запас на начало 90.115 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10579,7 +11166,7 @@
         <v>120</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2524141833335136</v>
+        <v>0.2524141833334994</v>
       </c>
     </row>
     <row r="3">
@@ -10600,12 +11187,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>запас после поступления 129.556 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-10 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 129.556 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-10 (поставка одной партией в начале месяца; запас на начало 99.419 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10642,12 +11229,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>запас после поступления 138.860 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-11 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 138.860 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-11 (поставка одной партией в начале месяца; запас на начало 108.723 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10721,7 +11308,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10731,23 +11318,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>запас на конец месяца 134.627 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
+          <t>пик запаса внутри месяца 148.164 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-12 (поставка одной партией в начале месяца; запас на начало 118.027 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>134.6273293500003</v>
+        <v>148.1636025833336</v>
       </c>
       <c r="J6" t="n">
         <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>14.62732935000025</v>
+        <v>28.16360258333356</v>
       </c>
     </row>
     <row r="7">
@@ -10773,23 +11360,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>запас на конец месяца 141.924 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
+          <t>запас на конец месяца 134.627 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2039</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>141.9243894500003</v>
+        <v>134.6273293500003</v>
       </c>
       <c r="J7" t="n">
         <v>120</v>
       </c>
       <c r="K7" t="n">
-        <v>21.92438945000026</v>
+        <v>14.62732935000025</v>
       </c>
     </row>
     <row r="8">
@@ -10805,7 +11392,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10815,23 +11402,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>запас на конец месяца 149.221 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
+          <t>пик запаса внутри месяца 161.294 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01 (поставка одной партией в начале месяца; запас на начало 127.330 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2039</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>149.2214495500003</v>
+        <v>161.2939960166669</v>
       </c>
       <c r="J8" t="n">
         <v>120</v>
       </c>
       <c r="K8" t="n">
-        <v>29.22144955000027</v>
+        <v>41.29399601666688</v>
       </c>
     </row>
     <row r="9">
@@ -10857,23 +11444,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>запас на конец месяца 156.519 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
+          <t>запас на конец месяца 141.924 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2039</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>156.5185096500003</v>
+        <v>141.9243894500003</v>
       </c>
       <c r="J9" t="n">
         <v>120</v>
       </c>
       <c r="K9" t="n">
-        <v>36.51850965000028</v>
+        <v>21.92438945000026</v>
       </c>
     </row>
     <row r="10">
@@ -10889,7 +11476,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10899,23 +11486,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>запас на конец месяца 163.816 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
+          <t>пик запаса внутри месяца 168.591 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02 (поставка одной партией в начале месяца; запас на начало 134.627 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2039</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>163.8155697500003</v>
+        <v>168.5910561166669</v>
       </c>
       <c r="J10" t="n">
         <v>120</v>
       </c>
       <c r="K10" t="n">
-        <v>43.81556975000029</v>
+        <v>48.59105611666692</v>
       </c>
     </row>
     <row r="11">
@@ -10941,23 +11528,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>запас на конец месяца 171.113 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
+          <t>запас на конец месяца 149.221 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2039</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>171.1126298500003</v>
+        <v>149.2214495500003</v>
       </c>
       <c r="J11" t="n">
         <v>120</v>
       </c>
       <c r="K11" t="n">
-        <v>51.1126298500003</v>
+        <v>29.22144955000027</v>
       </c>
     </row>
     <row r="12">
@@ -10973,7 +11560,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10983,23 +11570,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>запас на конец месяца 178.410 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
+          <t>пик запаса внутри месяца 175.888 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03 (поставка одной партией в начале месяца; запас на начало 141.924 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2039</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>178.4096899500003</v>
+        <v>175.8881162166669</v>
       </c>
       <c r="J12" t="n">
         <v>120</v>
       </c>
       <c r="K12" t="n">
-        <v>58.40968995000031</v>
+        <v>55.88811621666693</v>
       </c>
     </row>
     <row r="13">
@@ -11025,23 +11612,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>запас на конец месяца 185.707 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
+          <t>запас на конец месяца 156.519 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2039</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>185.7067500500003</v>
+        <v>156.5185096500003</v>
       </c>
       <c r="J13" t="n">
         <v>120</v>
       </c>
       <c r="K13" t="n">
-        <v>65.70675005000032</v>
+        <v>36.51850965000028</v>
       </c>
     </row>
     <row r="14">
@@ -11057,7 +11644,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11067,23 +11654,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>запас на конец месяца 193.004 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
+          <t>пик запаса внутри месяца 183.185 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04 (поставка одной партией в начале месяца; запас на начало 149.221 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2039</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>193.0038101500003</v>
+        <v>183.1851763166669</v>
       </c>
       <c r="J14" t="n">
         <v>120</v>
       </c>
       <c r="K14" t="n">
-        <v>73.00381015000033</v>
+        <v>63.18517631666694</v>
       </c>
     </row>
     <row r="15">
@@ -11109,23 +11696,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>запас на конец месяца 200.301 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
+          <t>запас на конец месяца 163.816 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2039</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>200.3008702500003</v>
+        <v>163.8155697500003</v>
       </c>
       <c r="J15" t="n">
         <v>120</v>
       </c>
       <c r="K15" t="n">
-        <v>80.30087025000034</v>
+        <v>43.81556975000029</v>
       </c>
     </row>
     <row r="16">
@@ -11141,7 +11728,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11151,23 +11738,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>запас на конец месяца 207.598 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
+          <t>пик запаса внутри месяца 190.482 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05 (поставка одной партией в начале месяца; запас на начало 156.519 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2039</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>207.5979303500004</v>
+        <v>190.482236416667</v>
       </c>
       <c r="J16" t="n">
         <v>120</v>
       </c>
       <c r="K16" t="n">
-        <v>87.59793035000035</v>
+        <v>70.48223641666695</v>
       </c>
     </row>
     <row r="17">
@@ -11193,23 +11780,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>запас на конец месяца 214.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
+          <t>запас на конец месяца 171.113 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2039</v>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>214.8949904500004</v>
+        <v>171.1126298500003</v>
       </c>
       <c r="J17" t="n">
         <v>120</v>
       </c>
       <c r="K17" t="n">
-        <v>94.89499045000036</v>
+        <v>51.1126298500003</v>
       </c>
     </row>
     <row r="18">
@@ -11225,7 +11812,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11235,23 +11822,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>запас на конец месяца 219.770 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
+          <t>пик запаса внутри месяца 197.779 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06 (поставка одной партией в начале месяца; запас на начало 163.816 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>219.7699930500004</v>
+        <v>197.779296516667</v>
       </c>
       <c r="J18" t="n">
         <v>120</v>
       </c>
       <c r="K18" t="n">
-        <v>99.76999305000035</v>
+        <v>77.77929651666696</v>
       </c>
     </row>
     <row r="19">
@@ -11277,23 +11864,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>запас на конец месяца 224.645 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
+          <t>запас на конец месяца 178.410 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>224.6449956500003</v>
+        <v>178.4096899500003</v>
       </c>
       <c r="J19" t="n">
         <v>120</v>
       </c>
       <c r="K19" t="n">
-        <v>104.6449956500003</v>
+        <v>58.40968995000031</v>
       </c>
     </row>
     <row r="20">
@@ -11309,7 +11896,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11319,23 +11906,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>запас на конец месяца 229.520 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
+          <t>пик запаса внутри месяца 205.076 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07 (поставка одной партией в начале месяца; запас на начало 171.113 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>229.5199982500004</v>
+        <v>205.076356616667</v>
       </c>
       <c r="J20" t="n">
         <v>120</v>
       </c>
       <c r="K20" t="n">
-        <v>109.5199982500004</v>
+        <v>85.07635661666697</v>
       </c>
     </row>
     <row r="21">
@@ -11361,23 +11948,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>запас на конец месяца 234.395 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
+          <t>запас на конец месяца 185.707 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>234.3950008500004</v>
+        <v>185.7067500500003</v>
       </c>
       <c r="J21" t="n">
         <v>120</v>
       </c>
       <c r="K21" t="n">
-        <v>114.3950008500004</v>
+        <v>65.70675005000032</v>
       </c>
     </row>
     <row r="22">
@@ -11393,7 +11980,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -11403,23 +11990,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>запас на конец месяца 239.270 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
+          <t>пик запаса внутри месяца 212.373 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08 (поставка одной партией в начале месяца; запас на начало 178.410 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>239.2700034500004</v>
+        <v>212.373416716667</v>
       </c>
       <c r="J22" t="n">
         <v>120</v>
       </c>
       <c r="K22" t="n">
-        <v>119.2700034500004</v>
+        <v>92.37341671666698</v>
       </c>
     </row>
     <row r="23">
@@ -11445,23 +12032,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>запас на конец месяца 244.145 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
+          <t>запас на конец месяца 193.004 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>244.1450060500004</v>
+        <v>193.0038101500003</v>
       </c>
       <c r="J23" t="n">
         <v>120</v>
       </c>
       <c r="K23" t="n">
-        <v>124.1450060500004</v>
+        <v>73.00381015000033</v>
       </c>
     </row>
     <row r="24">
@@ -11477,7 +12064,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11487,23 +12074,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>запас на конец месяца 249.020 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
+          <t>пик запаса внутри месяца 219.670 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09 (поставка одной партией в начале месяца; запас на начало 185.707 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>249.0200086500004</v>
+        <v>219.670476816667</v>
       </c>
       <c r="J24" t="n">
         <v>120</v>
       </c>
       <c r="K24" t="n">
-        <v>129.0200086500004</v>
+        <v>99.67047681666699</v>
       </c>
     </row>
     <row r="25">
@@ -11529,23 +12116,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>запас на конец месяца 253.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
+          <t>запас на конец месяца 200.301 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>253.8950112500004</v>
+        <v>200.3008702500003</v>
       </c>
       <c r="J25" t="n">
         <v>120</v>
       </c>
       <c r="K25" t="n">
-        <v>133.8950112500004</v>
+        <v>80.30087025000034</v>
       </c>
     </row>
     <row r="26">
@@ -11561,7 +12148,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -11571,23 +12158,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>запас на конец месяца 258.770 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
+          <t>пик запаса внутри месяца 226.968 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10 (поставка одной партией в начале месяца; запас на начало 193.004 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>258.7700138500005</v>
+        <v>226.967536916667</v>
       </c>
       <c r="J26" t="n">
         <v>120</v>
       </c>
       <c r="K26" t="n">
-        <v>138.7700138500005</v>
+        <v>106.967536916667</v>
       </c>
     </row>
     <row r="27">
@@ -11613,23 +12200,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>запас на конец месяца 263.645 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
+          <t>запас на конец месяца 207.598 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>263.6450164500005</v>
+        <v>207.5979303500004</v>
       </c>
       <c r="J27" t="n">
         <v>120</v>
       </c>
       <c r="K27" t="n">
-        <v>143.6450164500005</v>
+        <v>87.59793035000035</v>
       </c>
     </row>
     <row r="28">
@@ -11645,7 +12232,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11655,23 +12242,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>запас на конец месяца 268.520 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
+          <t>пик запаса внутри месяца 234.265 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11 (поставка одной партией в начале месяца; запас на начало 200.301 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G28" t="n">
         <v>11</v>
       </c>
       <c r="I28" t="n">
-        <v>268.5200190500005</v>
+        <v>234.264597016667</v>
       </c>
       <c r="J28" t="n">
         <v>120</v>
       </c>
       <c r="K28" t="n">
-        <v>148.5200190500005</v>
+        <v>114.264597016667</v>
       </c>
     </row>
     <row r="29">
@@ -11697,23 +12284,1073 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>запас на конец месяца 273.395 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
+          <t>запас на конец месяца 214.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G29" t="n">
         <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>273.3950216500005</v>
+        <v>214.8949904500004</v>
       </c>
       <c r="J29" t="n">
         <v>120</v>
       </c>
       <c r="K29" t="n">
+        <v>94.89499045000036</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 241.562 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12 (поставка одной партией в начале месяца; запас на начало 207.598 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" t="n">
+        <v>241.561657116667</v>
+      </c>
+      <c r="J30" t="n">
+        <v>120</v>
+      </c>
+      <c r="K30" t="n">
+        <v>121.561657116667</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 219.770 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>219.7699930500004</v>
+      </c>
+      <c r="J31" t="n">
+        <v>120</v>
+      </c>
+      <c r="K31" t="n">
+        <v>99.76999305000035</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 252.270 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01 (поставка одной партией в начале месяца; запас на начало 214.895 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>252.2699930500004</v>
+      </c>
+      <c r="J32" t="n">
+        <v>120</v>
+      </c>
+      <c r="K32" t="n">
+        <v>132.2699930500004</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 224.645 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>224.6449956500003</v>
+      </c>
+      <c r="J33" t="n">
+        <v>120</v>
+      </c>
+      <c r="K33" t="n">
+        <v>104.6449956500003</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 257.145 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02 (поставка одной партией в начале месяца; запас на начало 219.770 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>257.1449956500003</v>
+      </c>
+      <c r="J34" t="n">
+        <v>120</v>
+      </c>
+      <c r="K34" t="n">
+        <v>137.1449956500003</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 229.520 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>229.5199982500004</v>
+      </c>
+      <c r="J35" t="n">
+        <v>120</v>
+      </c>
+      <c r="K35" t="n">
+        <v>109.5199982500004</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 262.020 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03 (поставка одной партией в начале месяца; запас на начало 224.645 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>262.0199982500004</v>
+      </c>
+      <c r="J36" t="n">
+        <v>120</v>
+      </c>
+      <c r="K36" t="n">
+        <v>142.0199982500004</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 234.395 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>234.3950008500004</v>
+      </c>
+      <c r="J37" t="n">
+        <v>120</v>
+      </c>
+      <c r="K37" t="n">
+        <v>114.3950008500004</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 266.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04 (поставка одной партией в начале месяца; запас на начало 229.520 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>266.8950008500004</v>
+      </c>
+      <c r="J38" t="n">
+        <v>120</v>
+      </c>
+      <c r="K38" t="n">
+        <v>146.8950008500004</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 239.270 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>239.2700034500004</v>
+      </c>
+      <c r="J39" t="n">
+        <v>120</v>
+      </c>
+      <c r="K39" t="n">
+        <v>119.2700034500004</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 271.770 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05 (поставка одной партией в начале месяца; запас на начало 234.395 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>271.7700034500004</v>
+      </c>
+      <c r="J40" t="n">
+        <v>120</v>
+      </c>
+      <c r="K40" t="n">
+        <v>151.7700034500004</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 244.145 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>244.1450060500004</v>
+      </c>
+      <c r="J41" t="n">
+        <v>120</v>
+      </c>
+      <c r="K41" t="n">
+        <v>124.1450060500004</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 276.645 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06 (поставка одной партией в начале месяца; запас на начало 239.270 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>276.6450060500004</v>
+      </c>
+      <c r="J42" t="n">
+        <v>120</v>
+      </c>
+      <c r="K42" t="n">
+        <v>156.6450060500004</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 249.020 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" t="n">
+        <v>249.0200086500004</v>
+      </c>
+      <c r="J43" t="n">
+        <v>120</v>
+      </c>
+      <c r="K43" t="n">
+        <v>129.0200086500004</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 281.520 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07 (поставка одной партией в начале месяца; запас на начало 244.145 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G44" t="n">
+        <v>7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>281.5200086500004</v>
+      </c>
+      <c r="J44" t="n">
+        <v>120</v>
+      </c>
+      <c r="K44" t="n">
+        <v>161.5200086500004</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 253.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" t="n">
+        <v>253.8950112500004</v>
+      </c>
+      <c r="J45" t="n">
+        <v>120</v>
+      </c>
+      <c r="K45" t="n">
+        <v>133.8950112500004</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 286.395 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08 (поставка одной партией в начале месяца; запас на начало 249.020 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>286.3950112500004</v>
+      </c>
+      <c r="J46" t="n">
+        <v>120</v>
+      </c>
+      <c r="K46" t="n">
+        <v>166.3950112500004</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 258.770 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G47" t="n">
+        <v>9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>258.7700138500005</v>
+      </c>
+      <c r="J47" t="n">
+        <v>120</v>
+      </c>
+      <c r="K47" t="n">
+        <v>138.7700138500005</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 291.270 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09 (поставка одной партией в начале месяца; запас на начало 253.895 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="I48" t="n">
+        <v>291.2700138500005</v>
+      </c>
+      <c r="J48" t="n">
+        <v>120</v>
+      </c>
+      <c r="K48" t="n">
+        <v>171.2700138500005</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 263.645 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" t="n">
+        <v>263.6450164500005</v>
+      </c>
+      <c r="J49" t="n">
+        <v>120</v>
+      </c>
+      <c r="K49" t="n">
+        <v>143.6450164500005</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 296.145 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10 (поставка одной партией в начале месяца; запас на начало 258.770 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" t="n">
+        <v>296.1450164500005</v>
+      </c>
+      <c r="J50" t="n">
+        <v>120</v>
+      </c>
+      <c r="K50" t="n">
+        <v>176.1450164500005</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 268.520 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G51" t="n">
+        <v>11</v>
+      </c>
+      <c r="I51" t="n">
+        <v>268.5200190500005</v>
+      </c>
+      <c r="J51" t="n">
+        <v>120</v>
+      </c>
+      <c r="K51" t="n">
+        <v>148.5200190500005</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 301.020 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11 (поставка одной партией в начале месяца; запас на начало 263.645 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G52" t="n">
+        <v>11</v>
+      </c>
+      <c r="I52" t="n">
+        <v>301.0200190500005</v>
+      </c>
+      <c r="J52" t="n">
+        <v>120</v>
+      </c>
+      <c r="K52" t="n">
+        <v>181.0200190500005</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 273.395 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G53" t="n">
+        <v>12</v>
+      </c>
+      <c r="I53" t="n">
+        <v>273.3950216500005</v>
+      </c>
+      <c r="J53" t="n">
+        <v>120</v>
+      </c>
+      <c r="K53" t="n">
         <v>153.3950216500005</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 305.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12 (поставка одной партией в начале месяца; запас на начало 268.520 т, нетто-поступление 37.375 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G54" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>305.8950216500005</v>
+      </c>
+      <c r="J54" t="n">
+        <v>120</v>
+      </c>
+      <c r="K54" t="n">
+        <v>185.8950216500005</v>
       </c>
     </row>
   </sheetData>
@@ -11727,7 +13364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13418,7 +15055,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -13426,14 +15063,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -13450,7 +15087,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13467,7 +15104,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -13475,14 +15112,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -13516,7 +15153,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -13524,18 +15161,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -13545,7 +15183,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13560,7 +15202,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -13568,7 +15210,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -13604,27 +15246,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -13634,11 +15275,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13653,7 +15290,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -13661,14 +15298,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -13685,7 +15322,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13702,7 +15339,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -13710,14 +15347,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -13734,7 +15371,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13751,7 +15388,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -13759,170 +15396,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>27.71964825000006</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13937,7 +15574,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -13945,14 +15582,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>27.71964825000006</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -13969,7 +15606,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13986,7 +15623,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -13994,14 +15631,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>17.948</v>
+        <v>43.5529815833334</v>
       </c>
       <c r="G48" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14018,7 +15655,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14035,7 +15672,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -14043,14 +15680,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>17.9471</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>17.948</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14067,7 +15704,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14084,7 +15721,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -14092,219 +15729,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>17.948</v>
+      </c>
+      <c r="G51" t="n">
+        <v>130</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>17.9471</v>
+      </c>
+      <c r="G52" t="n">
+        <v>17.948</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>127.3302692500002</v>
-      </c>
-      <c r="G52" t="n">
-        <v>120</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>190</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>190</v>
-      </c>
-      <c r="G54" t="n">
-        <v>190</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -14319,7 +15956,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -14327,14 +15964,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>56.038</v>
+        <v>127.3302692500002</v>
       </c>
       <c r="G55" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -14342,7 +15979,7 @@
         </is>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -14351,7 +15988,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14368,7 +16005,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -14376,14 +16013,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>56.0372</v>
+        <v>148.1636025833336</v>
       </c>
       <c r="G56" t="n">
-        <v>56.038</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -14391,7 +16028,7 @@
         </is>
       </c>
       <c r="I56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -14400,7 +16037,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14425,14 +16062,14 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G57" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -14449,7 +16086,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14474,14 +16111,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -14498,7 +16135,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14515,7 +16152,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -14523,268 +16160,268 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>56.038</v>
+      </c>
+      <c r="G59" t="n">
+        <v>130</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>56.0372</v>
+      </c>
+      <c r="G60" t="n">
+        <v>56.038</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>120</v>
+      </c>
+      <c r="G61" t="n">
+        <v>120</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>100</v>
+      </c>
+      <c r="G62" t="n">
+        <v>100</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59">
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63">
         <f>=</f>
         <v/>
       </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D64" t="n">
         <v>2038</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60">
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64">
         <f>=</f>
         <v/>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>214.8949904500004</v>
-      </c>
-      <c r="G61" t="n">
-        <v>120</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>190</v>
-      </c>
-      <c r="G62" t="n">
-        <v>190</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>190</v>
-      </c>
-      <c r="G63" t="n">
-        <v>190</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>reserved_C_t_per_year</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>102.515</v>
-      </c>
-      <c r="G64" t="n">
-        <v>130</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Earth-New</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -14799,7 +16436,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -14807,14 +16444,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>102.5149</v>
+        <v>214.8949904500004</v>
       </c>
       <c r="G65" t="n">
-        <v>102.515</v>
+        <v>120</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -14822,7 +16459,7 @@
         </is>
       </c>
       <c r="I65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -14831,7 +16468,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14848,7 +16485,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -14856,11 +16493,11 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>120</v>
+        <v>241.561657116667</v>
       </c>
       <c r="G66" t="n">
         <v>120</v>
@@ -14871,7 +16508,7 @@
         </is>
       </c>
       <c r="I66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -14880,7 +16517,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14897,7 +16534,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -14905,14 +16542,14 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G67" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -14929,7 +16566,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14946,7 +16583,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -14954,317 +16591,317 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>190</v>
+      </c>
+      <c r="G68" t="n">
+        <v>190</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>102.515</v>
+      </c>
+      <c r="G69" t="n">
+        <v>130</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>102.5149</v>
+      </c>
+      <c r="G70" t="n">
+        <v>102.515</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>120</v>
+      </c>
+      <c r="G71" t="n">
+        <v>120</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>120</v>
+      </c>
+      <c r="G72" t="n">
+        <v>120</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68">
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73">
         <f>=</f>
         <v/>
       </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D74" t="n">
         <v>2039</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74">
         <f>=</f>
         <v/>
       </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>273.3950216500005</v>
-      </c>
-      <c r="G70" t="n">
-        <v>120</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>190</v>
-      </c>
-      <c r="G71" t="n">
-        <v>190</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>190</v>
-      </c>
-      <c r="G72" t="n">
-        <v>190</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>13.948</v>
-      </c>
-      <c r="G73" t="n">
-        <v>110</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>13.9474</v>
-      </c>
-      <c r="G74" t="n">
-        <v>13.948</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -15279,7 +16916,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -15287,14 +16924,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>130</v>
+        <v>273.3950216500005</v>
       </c>
       <c r="G75" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15302,7 +16939,7 @@
         </is>
       </c>
       <c r="I75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -15311,7 +16948,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15328,7 +16965,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -15336,14 +16973,14 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>130</v>
+        <v>305.8950216500005</v>
       </c>
       <c r="G76" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15351,7 +16988,7 @@
         </is>
       </c>
       <c r="I76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -15360,7 +16997,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -15385,14 +17022,14 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G77" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -15409,7 +17046,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -15434,14 +17071,14 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G78" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -15458,7 +17095,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -15475,7 +17112,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -15483,72 +17120,366 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>13.948</v>
+      </c>
+      <c r="G79" t="n">
+        <v>110</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>13.9474</v>
+      </c>
+      <c r="G80" t="n">
+        <v>13.948</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>130</v>
+      </c>
+      <c r="G81" t="n">
+        <v>130</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>130</v>
+      </c>
+      <c r="G82" t="n">
+        <v>130</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>120</v>
+      </c>
+      <c r="G83" t="n">
+        <v>120</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>120</v>
+      </c>
+      <c r="G84" t="n">
+        <v>120</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85">
         <f>=</f>
         <v/>
       </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>P4_full_adapted</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D86" t="n">
         <v>2040</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80">
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86">
         <f>=</f>
         <v/>
       </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25607,7 +27538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25649,7 +27580,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12773.153732239</v>
+        <v>12773.523598009</v>
       </c>
     </row>
     <row r="3">
@@ -25669,7 +27600,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10305.74253667026</v>
+        <v>10306.11240244026</v>
       </c>
     </row>
     <row r="4">
@@ -25809,7 +27740,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.189319231826619</v>
+        <v>9.189585322308634</v>
       </c>
     </row>
     <row r="11">
@@ -25829,7 +27760,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.414203263791551</v>
+        <v>7.414469354273566</v>
       </c>
     </row>
     <row r="12">
@@ -25989,7 +27920,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>397.5314022390007</v>
+        <v>397.9012680090007</v>
       </c>
     </row>
     <row r="20">
@@ -26105,11 +28036,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -26125,11 +28056,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -26145,11 +28076,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
@@ -26165,10 +28096,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26185,11 +28116,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -26205,11 +28136,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P4_full_adapted</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>76</v>
+      <c r="D32" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
